--- a/DataTables/Datas/#VSStage.xlsx
+++ b/DataTables/Datas/#VSStage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,27 +444,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>spawnIntervalSec</t>
+          <t>spawnRadius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>spawnCountPerWave</t>
+          <t>damageTextEntityId</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>spawnRadius</t>
+          <t>expBase</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>enemyId</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>damageTextEntityId</t>
+          <t>expStep</t>
         </is>
       </c>
     </row>
@@ -506,15 +501,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -548,27 +538,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>刷怪间隔(秒)</t>
+          <t>刷怪半径</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>每批刷怪数</t>
+          <t>伤害飘字实体id(#Entity)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>刷怪半径</t>
+          <t>升级经验曲线基数(1级-&gt;2级所需)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>本关刷的敌人id(#VSEnemy)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>伤害飘字实体id(#Entity)</t>
+          <t>升级经验曲线步长(每级递增)</t>
         </is>
       </c>
     </row>
@@ -588,19 +573,16 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>500002</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>201001</v>
-      </c>
-      <c r="J4" t="n">
-        <v>500002</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/#VSStage.xlsx
+++ b/DataTables/Datas/#VSStage.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,16 @@
           <t>expStep</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>fieldWidth</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fieldHeight</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +519,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,6 +574,16 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>升级经验曲线步长(每级递增)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>场地宽度(移动边界,世界单位,X)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>场地高度(移动边界,世界单位,Z)</t>
         </is>
       </c>
     </row>
@@ -583,6 +613,12 @@
       </c>
       <c r="I4" t="n">
         <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>48</v>
+      </c>
+      <c r="K4" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
